--- a/data/derived_data/2_RarefyData/Dataset_1/ps_rare_16S_D1bis_otu_table.xlsx
+++ b/data/derived_data/2_RarefyData/Dataset_1/ps_rare_16S_D1bis_otu_table.xlsx
@@ -12,11 +12,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
   <si>
     <t xml:space="preserve"/>
   </si>
   <si>
+    <t xml:space="preserve">MS_085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_087</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_090</t>
   </si>
   <si>
@@ -26,6 +32,12 @@
     <t xml:space="preserve">MS_092</t>
   </si>
   <si>
+    <t xml:space="preserve">MS_093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_097</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_099</t>
   </si>
   <si>
@@ -183,6 +195,9 @@
   </si>
   <si>
     <t xml:space="preserve">MS_283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_10</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_11</t>
@@ -710,31 +725,43 @@
       <c r="BE1" t="s">
         <v>56</v>
       </c>
+      <c r="BF1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B2" t="n">
-        <v>2846</v>
+        <v>3000</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>922</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>1860</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1626</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>560</v>
+        <v>1439</v>
       </c>
       <c r="H2" t="n">
-        <v>794</v>
+        <v>2588</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -746,13 +773,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>767</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -782,7 +809,7 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>2748</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -794,13 +821,13 @@
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>193</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>2128</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
         <v>0</v>
@@ -833,7 +860,7 @@
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>488</v>
+        <v>0</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
@@ -848,10 +875,10 @@
         <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>808</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -875,69 +902,81 @@
         <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>2836</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>315</v>
+        <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>179</v>
+        <v>0</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>2843</v>
       </c>
       <c r="E3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="H3" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1869</v>
       </c>
       <c r="J3" t="n">
-        <v>111</v>
+        <v>1666</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>518</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>793</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -958,34 +997,34 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2753</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>127</v>
+        <v>2129</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1003,28 +1042,28 @@
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
         <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>467</v>
       </c>
       <c r="AT3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1033,10 +1072,10 @@
         <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>810</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1048,18 +1087,30 @@
         <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
         <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>67</v>
+        <v>0</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>2851</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>330</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>202</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
@@ -1068,7 +1119,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -1083,22 +1134,22 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1110,10 +1161,10 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1140,16 +1191,16 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -1158,7 +1209,7 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1170,7 +1221,7 @@
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
@@ -1188,28 +1239,28 @@
         <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>3</v>
+        <v>107</v>
       </c>
       <c r="AU4" t="n">
         <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="AW4" t="n">
         <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
@@ -1228,11 +1279,23 @@
       </c>
       <c r="BE4" t="n">
         <v>0</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>17</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B5" t="n">
         <v>0</v>
@@ -1325,10 +1388,10 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
@@ -1379,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
@@ -1394,18 +1457,30 @@
         <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B6" t="n">
         <v>0</v>
@@ -1414,16 +1489,16 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>765</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>777</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>329</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1435,10 +1510,10 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>701</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>339</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1456,7 +1531,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>782</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1465,147 +1540,159 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH6" t="n">
         <v>63</v>
       </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>243</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>225</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>86</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2976</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>3000</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1399</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>676</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>127</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>1643</v>
-      </c>
-      <c r="BE6" t="n">
+      <c r="BI6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>2078</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>21</v>
+        <v>737</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1016</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>780</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>335</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1620,10 +1707,10 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>763</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>303</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1641,7 +1728,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>762</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -1650,7 +1737,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1662,7 +1749,7 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1713,25 +1800,25 @@
         <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AW7" t="n">
         <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>2980</v>
       </c>
       <c r="BA7" t="n">
         <v>0</v>
@@ -1740,194 +1827,218 @@
         <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>1402</v>
       </c>
       <c r="BE7" t="n">
+        <v>631</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>127</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>1637</v>
+      </c>
+      <c r="BI7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B8" t="n">
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>2235</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>510</v>
+        <v>26</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>3000</v>
+        <v>44</v>
       </c>
       <c r="J8" t="n">
-        <v>2375</v>
+        <v>18</v>
       </c>
       <c r="K8" t="n">
-        <v>2299</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2601</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1333</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>708</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2218</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2937</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2511</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>618</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>448</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2634</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2968</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>641</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>902</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>752</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>2512</v>
+        <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1932</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>2872</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>2646</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>1702</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>2653</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>3000</v>
+        <v>57</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1601</v>
+        <v>20</v>
       </c>
       <c r="BA8" t="n">
-        <v>2324</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>2873</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
         <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>969</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>690</v>
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B9" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -1936,168 +2047,180 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>229</v>
+        <v>3000</v>
       </c>
       <c r="F9" t="n">
-        <v>978</v>
+        <v>2263</v>
       </c>
       <c r="G9" t="n">
-        <v>413</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>190</v>
+        <v>313</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="J9" t="n">
-        <v>514</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>554</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2414</v>
       </c>
       <c r="O9" t="n">
-        <v>220</v>
+        <v>2237</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2650</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1302</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>670</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>2238</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2951</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2552</v>
       </c>
       <c r="AD9" t="n">
-        <v>109</v>
+        <v>642</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>460</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2663</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2962</v>
       </c>
       <c r="AH9" t="n">
-        <v>1971</v>
+        <v>658</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>890</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>755</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>2533</v>
       </c>
       <c r="AT9" t="n">
-        <v>31</v>
+        <v>1931</v>
       </c>
       <c r="AU9" t="n">
-        <v>65</v>
+        <v>2865</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>2632</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1676</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>2617</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="BC9" t="n">
         <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>1598</v>
       </c>
       <c r="BE9" t="n">
-        <v>56</v>
+        <v>2369</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>2873</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>970</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>688</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B10" t="n">
         <v>0</v>
@@ -2106,7 +2229,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -2115,31 +2238,31 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1462</v>
+        <v>381</v>
       </c>
       <c r="H10" t="n">
-        <v>1903</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>945</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>397</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>818</v>
+        <v>482</v>
       </c>
       <c r="O10" t="n">
-        <v>1978</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -2151,7 +2274,7 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -2169,13 +2292,13 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2302</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2476</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -2184,88 +2307,285 @@
         <v>0</v>
       </c>
       <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>92</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>2005</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>31</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>64</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1474</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1893</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>815</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2038</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>169</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2272</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2460</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
         <v>75</v>
       </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>2172</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>957</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>128</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>279</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>168</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>62</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>134</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>2008</v>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>2168</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>962</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>135</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>289</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>185</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>125</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>1964</v>
       </c>
     </row>
   </sheetData>
